--- a/sheets/국악이꽃피는나무/검수/진도아리랑(5관).xlsx
+++ b/sheets/국악이꽃피는나무/검수/진도아리랑(5관).xlsx
@@ -4526,7 +4526,7 @@
       <c r="L3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-汰j
+汰
 –</t>
         </is>
       </c>
@@ -4654,7 +4654,7 @@
       <c r="B5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-汰j</t>
+汰</t>
         </is>
       </c>
       <c r="C5" s="26" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="D5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">太j</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="E5" s="26" t="inlineStr">
@@ -4697,7 +4697,7 @@
       <c r="J5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-汰j
+汰
 –</t>
         </is>
       </c>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="J7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰j</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="K7" s="28" t="inlineStr">
@@ -4918,7 +4918,7 @@
       <c r="A8" s="0"/>
       <c r="B8" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰j
+          <t xml:space="preserve">汰
 –
 △</t>
         </is>
@@ -4936,7 +4936,7 @@
       <c r="E8" s="27"/>
       <c r="F8" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰j
+          <t xml:space="preserve">汰
 –
 △</t>
         </is>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="N8" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰j
+          <t xml:space="preserve">汰
 –
 △</t>
         </is>
@@ -5101,7 +5101,7 @@
       <c r="A10" s="0"/>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰j
+          <t xml:space="preserve">汰
 –
 潢</t>
         </is>
@@ -5126,7 +5126,7 @@
       <c r="F10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">c淋
-汰j
+汰
 –</t>
         </is>
       </c>
@@ -5138,7 +5138,7 @@
       <c r="H10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-汰j
+汰
 –</t>
         </is>
       </c>
@@ -5149,7 +5149,7 @@
       </c>
       <c r="J10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰j
+          <t xml:space="preserve">汰
 –
 潢</t>
         </is>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="L10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰j</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="M10" s="28" t="inlineStr">
@@ -5172,7 +5172,7 @@
       <c r="N10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">c淋
-汰j
+汰
 –</t>
         </is>
       </c>
@@ -5184,7 +5184,7 @@
       <c r="P10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-汰j
+汰
 –</t>
         </is>
       </c>
@@ -5208,7 +5208,7 @@
       </c>
       <c r="D11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰j</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="E11" s="26" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="H11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰j</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="I11" s="26" t="inlineStr">
@@ -5245,7 +5245,7 @@
       <c r="L11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">c淋
-汰j
+汰
 –</t>
         </is>
       </c>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="P11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰j</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="Q11" s="26" t="inlineStr">

--- a/sheets/국악이꽃피는나무/검수/진도아리랑(5관).xlsx
+++ b/sheets/국악이꽃피는나무/검수/진도아리랑(5관).xlsx
@@ -4425,28 +4425,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="67.8" customHeight="true">
+    <row r="2" ht="64.52" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="100.96" customHeight="true">
+    <row r="3" ht="96.05" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="100.96" customHeight="true">
+    <row r="4" ht="96.05" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="100.96" customHeight="true">
+    <row r="5" ht="96.05" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="23" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="100.96" customHeight="true">
+    <row r="6" ht="96.05" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="100.96" customHeight="true">
+    <row r="7" ht="96.05" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="100.96" customHeight="true">
+    <row r="8" ht="96.05" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="23" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="100.96" customHeight="true">
+    <row r="9" ht="96.05" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="100.96" customHeight="true">
+    <row r="10" ht="96.05" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="23" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="100.96" customHeight="true">
+    <row r="11" ht="96.05" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -5275,7 +5275,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="100.96" customHeight="true">
+    <row r="12" ht="96.05" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="100.96" customHeight="true">
+    <row r="13" ht="96.05" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="100.96" customHeight="true">
+    <row r="14" ht="96.05" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="27"/>
@@ -5520,6 +5520,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="59"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
 </worksheet>
 </file>